--- a/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20260907.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20260907.xlsx
@@ -1239,17 +1239,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>9910</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>豐泰</t>
+          <t>至上</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>36,840,000</t>
+          <t>27,972,899</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1261,17 +1261,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>8112</t>
+          <t>9910</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>至上</t>
+          <t>豐泰</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>27,972,899</t>
+          <t>36,840,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
